--- a/Outputs/Tests statistiques/Tests de liaisons qualitatives.xlsx
+++ b/Outputs/Tests statistiques/Tests de liaisons qualitatives.xlsx
@@ -1,37 +1,93 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+  <si>
+    <t>Couple testé</t>
+  </si>
+  <si>
+    <t>Statistique de chi2</t>
+  </si>
+  <si>
+    <t>p-valeur</t>
+  </si>
+  <si>
+    <t>Décision</t>
+  </si>
+  <si>
+    <t>segment x type_vehicule</t>
+  </si>
+  <si>
+    <t>categorie_mère x typepermis</t>
+  </si>
+  <si>
+    <t>categorie_mère x segment</t>
+  </si>
+  <si>
+    <t>categorie_mère x type_vehicule</t>
+  </si>
+  <si>
+    <t>segment x typepermis</t>
+  </si>
+  <si>
+    <t>type_vehicule x typepermis</t>
+  </si>
+  <si>
+    <t>categorie_mère x typeinter</t>
+  </si>
+  <si>
+    <t>segment x typeinter</t>
+  </si>
+  <si>
+    <t>type_vehicule x typeinter</t>
+  </si>
+  <si>
+    <t>typeinter x typepermis</t>
+  </si>
+  <si>
+    <t>Lien significatif (p &lt; 0.05)</t>
+  </si>
+  <si>
+    <t>Indépendance (Non significatif)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +102,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,217 +418,165 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Couple testé</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Statistique de chi2</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>p-valeur</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Décision</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>categorie_mère x segment</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>44658.12466062518</v>
-      </c>
-      <c r="C2" t="n">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Lien significatif (p &lt; 0.05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>categorie_mère x type_vehicule</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>43614.59325497047</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1851.351657024795</v>
+      </c>
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Lien significatif (p &lt; 0.05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>categorie_mère x typepermis</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>53482.77936902122</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Lien significatif (p &lt; 0.05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>segment x type_vehicule</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>123111.0987458249</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Lien significatif (p &lt; 0.05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>segment x typepermis</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>20676.28536856824</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Lien significatif (p &lt; 0.05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>type_vehicule x typepermis</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>19984.30381456988</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Lien significatif (p &lt; 0.05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>categorie_mère x typeinter</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1363.346651436423</v>
-      </c>
-      <c r="C8" t="n">
-        <v>7.965688694109026e-277</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Lien significatif (p &lt; 0.05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>type_vehicule x typeinter</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>120.7148383051527</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.450932910241746e-20</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Lien significatif (p &lt; 0.05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>segment x typeinter</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>95.94718869513156</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.516289750375791e-16</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Lien significatif (p &lt; 0.05)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>typeinter x typepermis</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>53.33988875132319</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.583643228782186e-07</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Lien significatif (p &lt; 0.05)</t>
-        </is>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>517.1397010216542</v>
+      </c>
+      <c r="C3">
+        <v>6.346801225301869E-89</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>447.0958259918645</v>
+      </c>
+      <c r="C4">
+        <v>1.237215732122354E-67</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>451.5815528051648</v>
+      </c>
+      <c r="C5">
+        <v>3.836232762075217E-64</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>108.5349768488793</v>
+      </c>
+      <c r="C6">
+        <v>3.630499823515972E-14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>95.39479595541908</v>
+      </c>
+      <c r="C7">
+        <v>1.811835196552093E-10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>83.12595518372214</v>
+      </c>
+      <c r="C8">
+        <v>2.41844145882639E-10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>49.70411822641058</v>
+      </c>
+      <c r="C9">
+        <v>3.025148072251111E-07</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>52.67273443334521</v>
+      </c>
+      <c r="C10">
+        <v>4.709904100144789E-07</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <v>3.586478329751057</v>
+      </c>
+      <c r="C11">
+        <v>0.8923754201806781</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Outputs/Tests statistiques/Tests de liaisons qualitatives.xlsx
+++ b/Outputs/Tests statistiques/Tests de liaisons qualitatives.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
   <si>
     <t>Couple testé</t>
   </si>
@@ -28,10 +28,46 @@
     <t>Décision</t>
   </si>
   <si>
+    <t>categorie_mère x contrat_id</t>
+  </si>
+  <si>
+    <t>categorie_mère x garantie</t>
+  </si>
+  <si>
+    <t>contrat_id x garantie</t>
+  </si>
+  <si>
+    <t>categorie_mère x typepermis</t>
+  </si>
+  <si>
+    <t>contrat_id x segment</t>
+  </si>
+  <si>
+    <t>contrat_id x typepermis</t>
+  </si>
+  <si>
+    <t>contrat_id x typeinter</t>
+  </si>
+  <si>
+    <t>contrat_id x type_vehicule</t>
+  </si>
+  <si>
     <t>segment x type_vehicule</t>
   </si>
   <si>
-    <t>categorie_mère x typepermis</t>
+    <t>segment x typeinter</t>
+  </si>
+  <si>
+    <t>type_vehicule x typeinter</t>
+  </si>
+  <si>
+    <t>categorie_mère x typeinter</t>
+  </si>
+  <si>
+    <t>garantie x type_vehicule</t>
+  </si>
+  <si>
+    <t>garantie x typepermis</t>
   </si>
   <si>
     <t>categorie_mère x segment</t>
@@ -40,28 +76,22 @@
     <t>categorie_mère x type_vehicule</t>
   </si>
   <si>
+    <t>garantie x segment</t>
+  </si>
+  <si>
+    <t>type_vehicule x typepermis</t>
+  </si>
+  <si>
+    <t>garantie x typeinter</t>
+  </si>
+  <si>
     <t>segment x typepermis</t>
   </si>
   <si>
-    <t>type_vehicule x typepermis</t>
-  </si>
-  <si>
-    <t>categorie_mère x typeinter</t>
-  </si>
-  <si>
-    <t>segment x typeinter</t>
-  </si>
-  <si>
-    <t>type_vehicule x typeinter</t>
-  </si>
-  <si>
     <t>typeinter x typepermis</t>
   </si>
   <si>
     <t>Lien significatif (p &lt; 0.05)</t>
-  </si>
-  <si>
-    <t>Indépendance (Non significatif)</t>
   </si>
 </sst>
 </file>
@@ -419,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -441,13 +471,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>1851.351657024795</v>
+        <v>40520</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -455,13 +485,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>517.1397010216542</v>
+        <v>3933.567807854249</v>
       </c>
       <c r="C3">
-        <v>6.346801225301869E-89</v>
+        <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -469,13 +499,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>447.0958259918645</v>
+        <v>38258.11509713133</v>
       </c>
       <c r="C4">
-        <v>1.237215732122354E-67</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -483,13 +513,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>451.5815528051648</v>
+        <v>2135.23254950492</v>
       </c>
       <c r="C5">
-        <v>3.836232762075217E-64</v>
+        <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -497,13 +527,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>108.5349768488793</v>
+        <v>21322.63523362469</v>
       </c>
       <c r="C6">
-        <v>3.630499823515972E-14</v>
+        <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -511,13 +541,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>95.39479595541908</v>
+        <v>19351.42819649981</v>
       </c>
       <c r="C7">
-        <v>1.811835196552093E-10</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -525,13 +555,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>83.12595518372214</v>
+        <v>10130</v>
       </c>
       <c r="C8">
-        <v>2.41844145882639E-10</v>
+        <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -539,13 +569,13 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>49.70411822641058</v>
+        <v>25132.55091093458</v>
       </c>
       <c r="C9">
-        <v>3.025148072251111E-07</v>
+        <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -553,13 +583,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>52.67273443334521</v>
+        <v>12716.05538091356</v>
       </c>
       <c r="C10">
-        <v>4.709904100144789E-07</v>
+        <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -567,13 +597,167 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>3.586478329751057</v>
+        <v>1276.657128475301</v>
       </c>
       <c r="C11">
-        <v>0.8923754201806781</v>
+        <v>4.169831357921779E-268</v>
       </c>
       <c r="D11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <v>1179.051192163554</v>
+      </c>
+      <c r="C12">
+        <v>5.614506181891326E-245</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
         <v>15</v>
+      </c>
+      <c r="B13">
+        <v>943.009742232151</v>
+      </c>
+      <c r="C13">
+        <v>1.763968870610353E-190</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>1010.165519770492</v>
+      </c>
+      <c r="C14">
+        <v>2.374459024979052E-149</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>894.8699485148184</v>
+      </c>
+      <c r="C15">
+        <v>9.336222151286606E-147</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>741.1158880436537</v>
+      </c>
+      <c r="C16">
+        <v>6.526710483301208E-130</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <v>694.2670751348068</v>
+      </c>
+      <c r="C17">
+        <v>1.95175405437003E-115</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18">
+        <v>764.9156295094799</v>
+      </c>
+      <c r="C18">
+        <v>6.206777906576751E-110</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19">
+        <v>450.0616851088366</v>
+      </c>
+      <c r="C19">
+        <v>3.677189679188769E-80</v>
+      </c>
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
+        <v>395.0122247489434</v>
+      </c>
+      <c r="C20">
+        <v>4.670197056632572E-63</v>
+      </c>
+      <c r="D20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21">
+        <v>221.5859158059855</v>
+      </c>
+      <c r="C21">
+        <v>5.761045417632963E-36</v>
+      </c>
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22">
+        <v>149.9383731995124</v>
+      </c>
+      <c r="C22">
+        <v>2.019690388827295E-28</v>
+      </c>
+      <c r="D22" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
